--- a/data/rubble-transfer/plan.xlsx
+++ b/data/rubble-transfer/plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="219" documentId="11_A6BF2E2CF2CA68D323205908F6291AA03A305B13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4D63C01-F6CB-42FB-A7F4-8E6431558342}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="11_A6BF2E2CF2CA68D323205908F6291AA03A305B13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34770786-0C71-4BFE-AB74-D7180BF44DC6}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,11 +731,11 @@
         <v>562000</v>
       </c>
       <c r="D5" s="6">
-        <v>700239</v>
+        <v>705686</v>
       </c>
       <c r="E5" s="8">
         <f>D5/C5</f>
-        <v>1.2459768683274022</v>
+        <v>1.2556690391459076</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>10</v>
@@ -790,11 +790,11 @@
       </c>
       <c r="D8" s="10">
         <f>SUM(D5:D7)</f>
-        <v>1198408</v>
+        <v>1203855</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="0"/>
-        <v>1.1305895838148654</v>
+        <v>1.1357283357783365</v>
       </c>
       <c r="F8" s="7"/>
     </row>
@@ -847,11 +847,11 @@
         <v>641500</v>
       </c>
       <c r="D11" s="6">
-        <v>610169</v>
+        <v>610539</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0.95115978176149651</v>
+        <v>0.95173655494933751</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>19</v>
@@ -866,11 +866,11 @@
         <v>50000</v>
       </c>
       <c r="D12" s="6">
-        <v>23409</v>
+        <v>22778</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" si="0"/>
-        <v>0.46817999999999999</v>
+        <v>0.45556000000000002</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>20</v>
@@ -887,11 +887,11 @@
       </c>
       <c r="D13" s="10">
         <f>SUM(D9:D12)</f>
-        <v>1182709.1000000001</v>
+        <v>1182448.1000000001</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" ref="E13" si="1">D13/C13</f>
-        <v>0.75568844943533064</v>
+        <v>0.75552168426433242</v>
       </c>
       <c r="F13" s="7"/>
     </row>
@@ -998,14 +998,14 @@
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="D19" s="6">
         <v>0</v>
       </c>
-      <c r="E19" s="8" t="e">
+      <c r="E19" s="8">
         <f>D19/C19</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>31</v>
@@ -1018,7 +1018,7 @@
       <c r="B20" s="16"/>
       <c r="C20" s="10">
         <f>SUM(C14:C19)</f>
-        <v>2193744</v>
+        <v>2843744</v>
       </c>
       <c r="D20" s="10">
         <f>SUM(D14:D19)</f>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="E20" s="8">
         <f t="shared" ref="E20:E21" si="2">D20/C20</f>
-        <v>8.8605142623751909E-2</v>
+        <v>6.8352495864606663E-2</v>
       </c>
       <c r="F20" s="7"/>
     </row>
@@ -1037,15 +1037,15 @@
       <c r="B21" s="14"/>
       <c r="C21" s="11">
         <f>C8+C13+C20</f>
-        <v>4818804</v>
+        <v>5468804</v>
       </c>
       <c r="D21" s="12">
         <f>D8+D13+D20</f>
-        <v>2575494.1</v>
+        <v>2580680.1</v>
       </c>
       <c r="E21" s="8">
         <f t="shared" si="2"/>
-        <v>0.5344674944239276</v>
+        <v>0.47189113012644085</v>
       </c>
       <c r="F21" s="9"/>
     </row>
